--- a/機器マスター_空調.xlsx
+++ b/機器マスター_空調.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4560" yWindow="4560" windowWidth="22690" windowHeight="16160" tabRatio="600" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KUCHO_KIKI_MASTER" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROOM_MASTER" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KUCHO_KIKI_MASTER'!$A$1:$AW$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KUCHO_KIKI_MASTER'!$A$1:$AW$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KANKI_MASTER'!$A$2:$Y$2</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.####"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -81,17 +81,23 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <charset val="128"/>
+      <family val="3"/>
       <color rgb="FF202020"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <color rgb="FF1F4E78"/>
       <sz val="10"/>
@@ -116,24 +122,15 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
       <family val="3"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
       <family val="3"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <sz val="6"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -181,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,13 +230,8 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -253,33 +245,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,8 +667,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.95"/>
+  <dimension ref="A1:AW38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -710,7 +694,7 @@
     <col width="28" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
+    <row r="1" ht="27.9" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
           <t>SYSTEM_TYPE</t>
@@ -1492,13 +1476,39 @@
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="17" t="n"/>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>スリムZR</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>2方向天井カセット形</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>2方向</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
           <t>PLZ-HRMP80LF6</t>
@@ -1506,7 +1516,7 @@
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>４方向天井カセット形(ｉ－スクエアタイプ)</t>
+          <t>２方向天井カセット形</t>
         </is>
       </c>
       <c r="L6" s="17" t="n"/>
@@ -1558,36 +1568,86 @@
           <t>VP-25</t>
         </is>
       </c>
-      <c r="AC6" s="17" t="n"/>
-      <c r="AD6" s="17" t="n"/>
-      <c r="AE6" s="17" t="n"/>
-      <c r="AF6" s="17" t="n"/>
-      <c r="AG6" s="17" t="n"/>
-      <c r="AH6" s="17" t="n"/>
-      <c r="AI6" s="17" t="n"/>
-      <c r="AJ6" s="17" t="n"/>
-      <c r="AK6" s="17" t="n"/>
-      <c r="AL6" s="17" t="n"/>
-      <c r="AM6" s="17" t="n"/>
-      <c r="AN6" s="17" t="n"/>
-      <c r="AO6" s="17" t="n"/>
-      <c r="AP6" s="17" t="n"/>
-      <c r="AQ6" s="17" t="n"/>
-      <c r="AR6" s="17" t="n"/>
-      <c r="AS6" s="17" t="n"/>
-      <c r="AT6" s="17" t="n"/>
-      <c r="AU6" s="17" t="n"/>
-      <c r="AV6" s="17" t="n"/>
+      <c r="AC6" s="17" t="inlineStr">
+        <is>
+          <t>PL-RP80LA22</t>
+        </is>
+      </c>
+      <c r="AD6" s="17" t="inlineStr">
+        <is>
+          <t>PUZ-HRMP80KA10</t>
+        </is>
+      </c>
+      <c r="AE6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="17" t="inlineStr">
+        <is>
+          <t>PAR-48MA</t>
+        </is>
+      </c>
+      <c r="AH6" s="17" t="inlineStr">
+        <is>
+          <t>CMP-P71LWEG7</t>
+        </is>
+      </c>
+      <c r="AI6" s="17" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ6" s="17" t="n">
+        <v>940</v>
+      </c>
+      <c r="AK6" s="17" t="n">
+        <v>650</v>
+      </c>
+      <c r="AL6" s="17" t="n">
+        <v>1338</v>
+      </c>
+      <c r="AM6" s="17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AN6" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO6" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP6" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="AQ6" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AR6" s="17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS6" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT6" s="17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU6" s="17" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV6" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="AW6" s="17" t="inlineStr">
         <is>
-          <t>PDF仕様表から転記。能力・消費電力等は定格標準値。</t>
+          <t>添付PDF仕様表に基づき更新。室内機質量26kg（パネル8kg別）。仕様書2026-02-21。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>空冷ヒートポンプ式パッケージエアコン</t>
+          <t>ハウジングエアコン</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -1595,13 +1655,35 @@
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>1方向天井カセット形</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>1方向</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t>MLZ-HX2822AS</t>
@@ -1609,7 +1691,7 @@
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>４方向天井カセット形(ｉ－スクエアタイプ)</t>
+          <t>１方向天井カセット形ハウジングエアコン</t>
         </is>
       </c>
       <c r="L7" s="17" t="n"/>
@@ -1639,10 +1721,8 @@
       <c r="V7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="17" t="inlineStr">
-        <is>
-          <t>1φ</t>
-        </is>
+      <c r="W7" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="X7" s="17" t="n">
         <v>200</v>
@@ -1663,29 +1743,71 @@
           <t>VP20</t>
         </is>
       </c>
-      <c r="AC7" s="17" t="n"/>
-      <c r="AD7" s="17" t="n"/>
-      <c r="AE7" s="17" t="n"/>
-      <c r="AF7" s="17" t="n"/>
+      <c r="AC7" s="17" t="inlineStr">
+        <is>
+          <t>MLZ-HX2822AS-IN</t>
+        </is>
+      </c>
+      <c r="AD7" s="17" t="inlineStr">
+        <is>
+          <t>MULZ-HX2822AS</t>
+        </is>
+      </c>
+      <c r="AE7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="AG7" s="17" t="n"/>
       <c r="AH7" s="17" t="n"/>
-      <c r="AI7" s="17" t="n"/>
-      <c r="AJ7" s="17" t="n"/>
-      <c r="AK7" s="17" t="n"/>
-      <c r="AL7" s="17" t="n"/>
-      <c r="AM7" s="17" t="n"/>
-      <c r="AN7" s="17" t="n"/>
-      <c r="AO7" s="17" t="n"/>
-      <c r="AP7" s="17" t="n"/>
-      <c r="AQ7" s="17" t="n"/>
-      <c r="AR7" s="17" t="n"/>
-      <c r="AS7" s="17" t="n"/>
-      <c r="AT7" s="17" t="n"/>
-      <c r="AU7" s="17" t="n"/>
-      <c r="AV7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n">
+        <v>185</v>
+      </c>
+      <c r="AJ7" s="17" t="n">
+        <v>1102</v>
+      </c>
+      <c r="AK7" s="17" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL7" s="17" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM7" s="17" t="n">
+        <v>800</v>
+      </c>
+      <c r="AN7" s="17" t="n">
+        <v>285</v>
+      </c>
+      <c r="AO7" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP7" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="AQ7" s="17" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AR7" s="17" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AS7" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT7" s="17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" s="17" t="inlineStr">
+        <is>
+          <t>R410A</t>
+        </is>
+      </c>
+      <c r="AV7" s="17" t="n">
+        <v>1.1</v>
+      </c>
       <c r="AW7" s="17" t="inlineStr">
         <is>
-          <t>PDF仕様表から転記。能力・消費電力等は定格値。</t>
+          <t>添付PDF仕様表に基づき更新。室内送風機30W、室外50W。パネル3.4kg別。</t>
         </is>
       </c>
     </row>
@@ -1700,13 +1822,39 @@
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>スリムZR</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>1方向天井カセット形</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>1方向</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>同時ツイン</t>
+        </is>
+      </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
           <t>PMZX-HRMP80F6</t>
@@ -1714,7 +1862,7 @@
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
-          <t>４方向天井カセット形(ｉ－スクエアタイプ)</t>
+          <t>１方向天井カセット形／(同時ツイン同容量同タイプ)</t>
         </is>
       </c>
       <c r="L8" s="17" t="n"/>
@@ -1766,29 +1914,79 @@
           <t>VP-25</t>
         </is>
       </c>
-      <c r="AC8" s="17" t="n"/>
-      <c r="AD8" s="17" t="n"/>
-      <c r="AE8" s="17" t="n"/>
-      <c r="AF8" s="17" t="n"/>
-      <c r="AG8" s="17" t="n"/>
-      <c r="AH8" s="17" t="n"/>
-      <c r="AI8" s="17" t="n"/>
-      <c r="AJ8" s="17" t="n"/>
-      <c r="AK8" s="17" t="n"/>
-      <c r="AL8" s="17" t="n"/>
-      <c r="AM8" s="17" t="n"/>
-      <c r="AN8" s="17" t="n"/>
-      <c r="AO8" s="17" t="n"/>
-      <c r="AP8" s="17" t="n"/>
-      <c r="AQ8" s="17" t="n"/>
-      <c r="AR8" s="17" t="n"/>
-      <c r="AS8" s="17" t="n"/>
-      <c r="AT8" s="17" t="n"/>
-      <c r="AU8" s="17" t="n"/>
-      <c r="AV8" s="17" t="n"/>
+      <c r="AC8" s="17" t="inlineStr">
+        <is>
+          <t>PM-RP40FA22</t>
+        </is>
+      </c>
+      <c r="AD8" s="17" t="inlineStr">
+        <is>
+          <t>PUZ-HRMP80KA10</t>
+        </is>
+      </c>
+      <c r="AE8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="17" t="inlineStr">
+        <is>
+          <t>PAR-48MA</t>
+        </is>
+      </c>
+      <c r="AH8" s="17" t="inlineStr">
+        <is>
+          <t>PMP-P80FWH11</t>
+        </is>
+      </c>
+      <c r="AI8" s="17" t="n">
+        <v>225</v>
+      </c>
+      <c r="AJ8" s="17" t="n">
+        <v>1112</v>
+      </c>
+      <c r="AK8" s="17" t="n">
+        <v>724</v>
+      </c>
+      <c r="AL8" s="17" t="n">
+        <v>1338</v>
+      </c>
+      <c r="AM8" s="17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AN8" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO8" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP8" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="AQ8" s="17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR8" s="17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS8" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" s="17" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV8" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="AW8" s="17" t="inlineStr">
         <is>
-          <t>同時ツイン。室内機PM-RP40FA22×2台。室内送風機出力0.090kWは1台分。冷媒管径は室外側を記載。PDF仕様表から転記。</t>
+          <t>添付PDF仕様表に基づき更新。室内送風機0.09kWと質量25kgは1台分。分岐SDD-50SR9。室内側冷媒φ6.35/12.7、登録は室外側。</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4398,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="409.6" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>パッケージエアコン</t>
@@ -4365,7 +4563,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="409.6" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
@@ -4532,7 +4730,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="409.6" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>マルチエアコン</t>
@@ -4677,7 +4875,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="409.6" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
@@ -4802,7 +5000,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="409.6" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
@@ -4927,684 +5125,1643 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+    <row r="28" ht="409.6" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D28" s="38" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E28" s="37" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>ZXV</t>
         </is>
       </c>
-      <c r="F28" s="37" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>壁掛形</t>
         </is>
       </c>
-      <c r="G28" s="37" t="n"/>
-      <c r="H28" s="37" t="n">
+      <c r="G28" s="26" t="n"/>
+      <c r="H28" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="I28" s="37" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>シングル</t>
         </is>
       </c>
-      <c r="J28" s="37" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV22F1-W</t>
         </is>
       </c>
-      <c r="K28" s="37" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="L28" s="37" t="n"/>
-      <c r="M28" s="37" t="n"/>
-      <c r="N28" s="37" t="n"/>
-      <c r="O28" s="37" t="n">
+      <c r="L28" s="26" t="n"/>
+      <c r="M28" s="26" t="n"/>
+      <c r="N28" s="26" t="n"/>
+      <c r="O28" s="26" t="n">
         <v>2.2</v>
       </c>
-      <c r="P28" s="37" t="n">
+      <c r="P28" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q28" s="37" t="n">
+      <c r="Q28" s="26" t="n">
         <v>0.425</v>
       </c>
-      <c r="R28" s="37" t="n">
+      <c r="R28" s="26" t="n">
         <v>0.465</v>
       </c>
-      <c r="S28" s="37" t="n">
+      <c r="S28" s="26" t="n">
         <v>0.6</v>
       </c>
-      <c r="T28" s="37" t="n">
+      <c r="T28" s="26" t="n">
         <v>0.028</v>
       </c>
-      <c r="U28" s="37" t="n">
+      <c r="U28" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="V28" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" s="37" t="inlineStr">
+      <c r="V28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" s="26" t="inlineStr">
         <is>
           <t>1φ</t>
         </is>
       </c>
-      <c r="X28" s="37" t="n">
+      <c r="X28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="Y28" s="37" t="inlineStr">
+      <c r="Y28" s="26" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Z28" s="37" t="n">
+      <c r="Z28" s="26" t="n">
         <v>6.35</v>
       </c>
-      <c r="AA28" s="37" t="n">
+      <c r="AA28" s="26" t="n">
         <v>9.52</v>
       </c>
-      <c r="AB28" s="37" t="inlineStr">
+      <c r="AB28" s="26" t="inlineStr">
         <is>
           <t>φ16</t>
         </is>
       </c>
-      <c r="AC28" s="37" t="inlineStr">
+      <c r="AC28" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV22F1-W-IN</t>
         </is>
       </c>
-      <c r="AD28" s="37" t="inlineStr">
+      <c r="AD28" s="26" t="inlineStr">
         <is>
           <t>MUZ-ZXV22F1</t>
         </is>
       </c>
-      <c r="AE28" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="37" t="n"/>
-      <c r="AH28" s="37" t="n"/>
-      <c r="AI28" s="37" t="n">
+      <c r="AE28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="26" t="n"/>
+      <c r="AH28" s="26" t="n"/>
+      <c r="AI28" s="26" t="n">
         <v>295</v>
       </c>
-      <c r="AJ28" s="37" t="n">
+      <c r="AJ28" s="26" t="n">
         <v>799</v>
       </c>
-      <c r="AK28" s="37" t="n">
+      <c r="AK28" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="AL28" s="37" t="n">
+      <c r="AL28" s="26" t="n">
         <v>550</v>
       </c>
-      <c r="AM28" s="37" t="n">
+      <c r="AM28" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="AN28" s="37" t="n">
+      <c r="AN28" s="26" t="n">
         <v>285</v>
       </c>
-      <c r="AO28" s="37" t="n">
+      <c r="AO28" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="AP28" s="37" t="n">
+      <c r="AP28" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="AQ28" s="37" t="n">
+      <c r="AQ28" s="26" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR28" s="37" t="n">
+      <c r="AR28" s="26" t="n">
         <v>4.69</v>
       </c>
-      <c r="AS28" s="37" t="n">
+      <c r="AS28" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="AT28" s="37" t="n">
+      <c r="AT28" s="26" t="n">
         <v>6.9</v>
       </c>
-      <c r="AU28" s="37" t="inlineStr">
+      <c r="AU28" s="26" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="AV28" s="37" t="n">
+      <c r="AV28" s="26" t="n">
         <v>0.67</v>
       </c>
-      <c r="AW28" s="37" t="inlineStr">
+      <c r="AW28" s="26" t="inlineStr">
         <is>
           <t>出典: RAC-1（２２）新型RAC仕様書-1.pdf。50/60Hz共通。冷房2.2kW・425W・4.50A、暖房2.5kW・465W・4.69A（最大15.0A）。室内送風機28W、室外送風機50W、圧縮機呼称出力600W。室内機寸法は本体295×799×389mm（据付板含み394mm）、室外機寸法は本体550×800×285mm（突起部除く）。仕様書発行日2026-09-08。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+    <row r="29" ht="409.6" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>ZXV</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>壁掛形</t>
         </is>
       </c>
-      <c r="G29" s="37" t="n"/>
-      <c r="H29" s="37" t="n">
+      <c r="G29" s="26" t="n"/>
+      <c r="H29" s="26" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="37" t="inlineStr">
+      <c r="I29" s="26" t="inlineStr">
         <is>
           <t>シングル</t>
         </is>
       </c>
-      <c r="J29" s="37" t="inlineStr">
+      <c r="J29" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV25F1-W</t>
         </is>
       </c>
-      <c r="K29" s="37" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="L29" s="37" t="n"/>
-      <c r="M29" s="37" t="n"/>
-      <c r="N29" s="37" t="n"/>
-      <c r="O29" s="37" t="n">
+      <c r="L29" s="26" t="n"/>
+      <c r="M29" s="26" t="n"/>
+      <c r="N29" s="26" t="n"/>
+      <c r="O29" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="P29" s="37" t="n">
+      <c r="P29" s="26" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q29" s="37" t="n">
+      <c r="Q29" s="26" t="n">
         <v>0.5</v>
       </c>
-      <c r="R29" s="37" t="n">
+      <c r="R29" s="26" t="n">
         <v>0.525</v>
       </c>
-      <c r="S29" s="37" t="n">
+      <c r="S29" s="26" t="n">
         <v>0.65</v>
       </c>
-      <c r="T29" s="37" t="n">
+      <c r="T29" s="26" t="n">
         <v>0.028</v>
       </c>
-      <c r="U29" s="37" t="n">
+      <c r="U29" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="V29" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" s="37" t="inlineStr">
+      <c r="V29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" s="26" t="inlineStr">
         <is>
           <t>1φ</t>
         </is>
       </c>
-      <c r="X29" s="37" t="n">
+      <c r="X29" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="Y29" s="37" t="inlineStr">
+      <c r="Y29" s="26" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Z29" s="37" t="n">
+      <c r="Z29" s="26" t="n">
         <v>6.35</v>
       </c>
-      <c r="AA29" s="37" t="n">
+      <c r="AA29" s="26" t="n">
         <v>9.52</v>
       </c>
-      <c r="AB29" s="37" t="inlineStr">
+      <c r="AB29" s="26" t="inlineStr">
         <is>
           <t>φ16</t>
         </is>
       </c>
-      <c r="AC29" s="37" t="inlineStr">
+      <c r="AC29" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV25F1-W-IN</t>
         </is>
       </c>
-      <c r="AD29" s="37" t="inlineStr">
+      <c r="AD29" s="26" t="inlineStr">
         <is>
           <t>MUZ-ZXV25F1</t>
         </is>
       </c>
-      <c r="AE29" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="37" t="n"/>
-      <c r="AH29" s="37" t="n"/>
-      <c r="AI29" s="37" t="n">
+      <c r="AE29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="26" t="n"/>
+      <c r="AH29" s="26" t="n"/>
+      <c r="AI29" s="26" t="n">
         <v>295</v>
       </c>
-      <c r="AJ29" s="37" t="n">
+      <c r="AJ29" s="26" t="n">
         <v>799</v>
       </c>
-      <c r="AK29" s="37" t="n">
+      <c r="AK29" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="AL29" s="37" t="n">
+      <c r="AL29" s="26" t="n">
         <v>550</v>
       </c>
-      <c r="AM29" s="37" t="n">
+      <c r="AM29" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="AN29" s="37" t="n">
+      <c r="AN29" s="26" t="n">
         <v>285</v>
       </c>
-      <c r="AO29" s="37" t="n">
+      <c r="AO29" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="AP29" s="37" t="n">
+      <c r="AP29" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="AQ29" s="37" t="n">
+      <c r="AQ29" s="26" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR29" s="37" t="n">
+      <c r="AR29" s="26" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS29" s="37" t="n">
+      <c r="AS29" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="AT29" s="37" t="n">
+      <c r="AT29" s="26" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU29" s="37" t="inlineStr">
+      <c r="AU29" s="26" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="AV29" s="37" t="n">
+      <c r="AV29" s="26" t="n">
         <v>0.67</v>
       </c>
-      <c r="AW29" s="37" t="inlineStr">
+      <c r="AW29" s="26" t="inlineStr">
         <is>
           <t>出典: RAC-2（２５）新型RAC仕様書-2.pdf。50/60Hz共通。冷房2.5kW・500W・5.30A、暖房2.8kW・525W・5.30A（最大15.0A）。室内送風機28W、室外送風機50W、圧縮機呼称出力650W。室内機寸法は本体295×799×389mm（据付板含み394mm）、室外機寸法は本体550×800×285mm（突起部除く）。仕様書発行日2026-09-08。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+    <row r="30" ht="409.6" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>ZXV</t>
         </is>
       </c>
-      <c r="F30" s="37" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>壁掛形</t>
         </is>
       </c>
-      <c r="G30" s="37" t="n"/>
-      <c r="H30" s="37" t="n">
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="I30" s="37" t="inlineStr">
+      <c r="I30" s="26" t="inlineStr">
         <is>
           <t>シングル</t>
         </is>
       </c>
-      <c r="J30" s="37" t="inlineStr">
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV28F1-W</t>
         </is>
       </c>
-      <c r="K30" s="37" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="L30" s="37" t="n"/>
-      <c r="M30" s="37" t="n"/>
-      <c r="N30" s="37" t="n"/>
-      <c r="O30" s="37" t="n">
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="26" t="n"/>
+      <c r="N30" s="26" t="n"/>
+      <c r="O30" s="26" t="n">
         <v>2.8</v>
       </c>
-      <c r="P30" s="37" t="n">
+      <c r="P30" s="26" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q30" s="37" t="n">
+      <c r="Q30" s="26" t="n">
         <v>0.58</v>
       </c>
-      <c r="R30" s="37" t="n">
+      <c r="R30" s="26" t="n">
         <v>0.71</v>
       </c>
-      <c r="S30" s="37" t="n">
+      <c r="S30" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="T30" s="37" t="n">
+      <c r="T30" s="26" t="n">
         <v>0.028</v>
       </c>
-      <c r="U30" s="37" t="n">
+      <c r="U30" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="V30" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" s="37" t="inlineStr">
+      <c r="V30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" s="26" t="inlineStr">
         <is>
           <t>1φ</t>
         </is>
       </c>
-      <c r="X30" s="37" t="n">
+      <c r="X30" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="Y30" s="37" t="inlineStr">
+      <c r="Y30" s="26" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Z30" s="37" t="n">
+      <c r="Z30" s="26" t="n">
         <v>6.35</v>
       </c>
-      <c r="AA30" s="37" t="n">
+      <c r="AA30" s="26" t="n">
         <v>9.52</v>
       </c>
-      <c r="AB30" s="37" t="inlineStr">
+      <c r="AB30" s="26" t="inlineStr">
         <is>
           <t>φ16</t>
         </is>
       </c>
-      <c r="AC30" s="37" t="inlineStr">
+      <c r="AC30" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV28F1-W-IN</t>
         </is>
       </c>
-      <c r="AD30" s="37" t="inlineStr">
+      <c r="AD30" s="26" t="inlineStr">
         <is>
           <t>MUZ-ZXV28F1</t>
         </is>
       </c>
-      <c r="AE30" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="37" t="n"/>
-      <c r="AH30" s="37" t="n"/>
-      <c r="AI30" s="37" t="n">
+      <c r="AE30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="26" t="n"/>
+      <c r="AH30" s="26" t="n"/>
+      <c r="AI30" s="26" t="n">
         <v>295</v>
       </c>
-      <c r="AJ30" s="37" t="n">
+      <c r="AJ30" s="26" t="n">
         <v>799</v>
       </c>
-      <c r="AK30" s="37" t="n">
+      <c r="AK30" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="AL30" s="37" t="n">
+      <c r="AL30" s="26" t="n">
         <v>550</v>
       </c>
-      <c r="AM30" s="37" t="n">
+      <c r="AM30" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="AN30" s="37" t="n">
+      <c r="AN30" s="26" t="n">
         <v>285</v>
       </c>
-      <c r="AO30" s="37" t="n">
+      <c r="AO30" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="AP30" s="37" t="n">
+      <c r="AP30" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="AQ30" s="37" t="n">
+      <c r="AQ30" s="26" t="n">
         <v>6.17</v>
       </c>
-      <c r="AR30" s="37" t="n">
+      <c r="AR30" s="26" t="n">
         <v>7.17</v>
       </c>
-      <c r="AS30" s="37" t="n">
+      <c r="AS30" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="AT30" s="37" t="n">
+      <c r="AT30" s="26" t="n">
         <v>6.9</v>
       </c>
-      <c r="AU30" s="37" t="inlineStr">
+      <c r="AU30" s="26" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="AV30" s="37" t="n">
+      <c r="AV30" s="26" t="n">
         <v>0.87</v>
       </c>
-      <c r="AW30" s="37" t="inlineStr">
+      <c r="AW30" s="26" t="inlineStr">
         <is>
           <t>出典: RAC-3（２８）新型RAC仕様書-3.pdf。50/60Hz共通。冷房2.8kW・580W・6.17A、暖房3.6kW・710W・7.17A（最大20.0A）。室内送風機28W、室外送風機50W、圧縮機呼称出力750W。室内機寸法は本体295×799×389mm（据付板含み394mm）、室外機寸法は本体550×800×285mm（突起部除く）。仕様書発行日2026-09-08。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+    <row r="31" ht="409.6" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C31" s="37" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>ZXV</t>
         </is>
       </c>
-      <c r="F31" s="37" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>壁掛形</t>
         </is>
       </c>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="37" t="n">
+      <c r="G31" s="26" t="n"/>
+      <c r="H31" s="26" t="n">
         <v>71</v>
       </c>
-      <c r="I31" s="37" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
         <is>
           <t>シングル</t>
         </is>
       </c>
-      <c r="J31" s="37" t="inlineStr">
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV71F1S-W</t>
         </is>
       </c>
-      <c r="K31" s="37" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>冷暖房用壁掛形ルームエアコン</t>
         </is>
       </c>
-      <c r="L31" s="37" t="n"/>
-      <c r="M31" s="37" t="n"/>
-      <c r="N31" s="37" t="n"/>
-      <c r="O31" s="37" t="n">
+      <c r="L31" s="26" t="n"/>
+      <c r="M31" s="26" t="n"/>
+      <c r="N31" s="26" t="n"/>
+      <c r="O31" s="26" t="n">
         <v>7.1</v>
       </c>
-      <c r="P31" s="37" t="n">
+      <c r="P31" s="26" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q31" s="37" t="n">
+      <c r="Q31" s="26" t="n">
         <v>2.38</v>
       </c>
-      <c r="R31" s="37" t="n">
+      <c r="R31" s="26" t="n">
         <v>2.22</v>
       </c>
-      <c r="S31" s="37" t="n">
+      <c r="S31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="37" t="n">
+      <c r="T31" s="26" t="n">
         <v>0.046</v>
       </c>
-      <c r="U31" s="37" t="n">
+      <c r="U31" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="V31" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" s="37" t="inlineStr">
+      <c r="V31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="26" t="inlineStr">
         <is>
           <t>1φ</t>
         </is>
       </c>
-      <c r="X31" s="37" t="n">
+      <c r="X31" s="26" t="n">
         <v>200</v>
       </c>
-      <c r="Y31" s="37" t="inlineStr">
+      <c r="Y31" s="26" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Z31" s="37" t="n">
+      <c r="Z31" s="26" t="n">
         <v>6.35</v>
       </c>
-      <c r="AA31" s="37" t="n">
+      <c r="AA31" s="26" t="n">
         <v>12.7</v>
       </c>
-      <c r="AB31" s="37" t="inlineStr">
+      <c r="AB31" s="26" t="inlineStr">
         <is>
           <t>φ16</t>
         </is>
       </c>
-      <c r="AC31" s="37" t="inlineStr">
+      <c r="AC31" s="26" t="inlineStr">
         <is>
           <t>MSZ-ZXV71F1S-W-IN</t>
         </is>
       </c>
-      <c r="AD31" s="37" t="inlineStr">
+      <c r="AD31" s="26" t="inlineStr">
         <is>
           <t>MUZ-ZXV71F1S</t>
         </is>
       </c>
-      <c r="AE31" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="37" t="n"/>
-      <c r="AH31" s="37" t="n"/>
-      <c r="AI31" s="37" t="n">
+      <c r="AE31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="26" t="n"/>
+      <c r="AH31" s="26" t="n"/>
+      <c r="AI31" s="26" t="n">
         <v>295</v>
       </c>
-      <c r="AJ31" s="37" t="n">
+      <c r="AJ31" s="26" t="n">
         <v>799</v>
       </c>
-      <c r="AK31" s="37" t="n">
+      <c r="AK31" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="AL31" s="37" t="n">
+      <c r="AL31" s="26" t="n">
         <v>714</v>
       </c>
-      <c r="AM31" s="37" t="n">
+      <c r="AM31" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="AN31" s="37" t="n">
+      <c r="AN31" s="26" t="n">
         <v>285</v>
       </c>
-      <c r="AO31" s="37" t="n">
+      <c r="AO31" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="AP31" s="37" t="n">
+      <c r="AP31" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="AQ31" s="37" t="n">
+      <c r="AQ31" s="26" t="n">
         <v>12.65</v>
       </c>
-      <c r="AR31" s="37" t="n">
+      <c r="AR31" s="26" t="n">
         <v>11.2</v>
       </c>
-      <c r="AS31" s="37" t="n">
+      <c r="AS31" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="AT31" s="37" t="n">
+      <c r="AT31" s="26" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU31" s="37" t="inlineStr">
+      <c r="AU31" s="26" t="inlineStr">
         <is>
           <t>R32</t>
         </is>
       </c>
-      <c r="AV31" s="37" t="n">
+      <c r="AV31" s="26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AW31" s="37" t="inlineStr">
+      <c r="AW31" s="26" t="inlineStr">
         <is>
           <t>出典: RAC-4（７１）新型RAC仕様書-4.pdf。50/60Hz共通。単相200V。冷房7.1kW・2.380kW・12.65A、暖房8.5kW・2.220kW・11.20A（最大20.0A）。室内送風機46W、室外送風機50W、圧縮機呼称出力2.0kW。室内機寸法は本体295×799×389mm（据付板含み394mm）、室外機寸法は本体714×800×285mm（突起部除く）。仕様書発行日2026-09-08。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
     </row>
+    <row r="32" ht="92.40000000000001" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>空冷ヒートポンプ式パッケージエアコン</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>三菱電機</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>スリムZR</t>
+        </is>
+      </c>
+      <c r="F32" s="26" t="inlineStr">
+        <is>
+          <t>天吊形</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>天吊形</t>
+        </is>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>160</v>
+      </c>
+      <c r="I32" s="26" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
+      <c r="J32" s="26" t="inlineStr">
+        <is>
+          <t>PCZ-HRMP160K6</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>天吊形(ワイヤード)</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n"/>
+      <c r="M32" s="26" t="n"/>
+      <c r="N32" s="26" t="n"/>
+      <c r="O32" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="P32" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="26" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="S32" s="26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T32" s="26" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U32" s="26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V32" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" s="26" t="inlineStr">
+        <is>
+          <t>3φ</t>
+        </is>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y32" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z32" s="26" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AA32" s="26" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="AB32" s="26" t="inlineStr">
+        <is>
+          <t>VP-20</t>
+        </is>
+      </c>
+      <c r="AC32" s="26" t="inlineStr">
+        <is>
+          <t>PC-RP160KA22</t>
+        </is>
+      </c>
+      <c r="AD32" s="26" t="inlineStr">
+        <is>
+          <t>PUZ-HRMP160KA10</t>
+        </is>
+      </c>
+      <c r="AE32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="26" t="inlineStr">
+        <is>
+          <t>PAR-48MA</t>
+        </is>
+      </c>
+      <c r="AH32" s="26" t="n"/>
+      <c r="AI32" s="26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ32" s="26" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AK32" s="26" t="n">
+        <v>680</v>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>1338</v>
+      </c>
+      <c r="AM32" s="26" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AN32" s="26" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO32" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP32" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="AQ32" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR32" s="26" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AS32" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT32" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU32" s="26" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV32" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW32" s="26" t="inlineStr">
+        <is>
+          <t>添付PDF仕様表から登録。定格標準値。仕様書2026-02-21。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="105.6" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>ルームエアコン</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>三菱電機</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>壁掛形</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>壁掛形</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>MSZ-NXV2226-W</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>冷暖房用壁掛形ルームエアコン</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n"/>
+      <c r="M33" s="26" t="n"/>
+      <c r="N33" s="26" t="n"/>
+      <c r="O33" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P33" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q33" s="26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="S33" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T33" s="26" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="U33" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y33" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z33" s="26" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA33" s="26" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AB33" s="26" t="inlineStr">
+        <is>
+          <t>φ16（外径）</t>
+        </is>
+      </c>
+      <c r="AC33" s="26" t="inlineStr">
+        <is>
+          <t>MSZ-NXV2226-W-IN</t>
+        </is>
+      </c>
+      <c r="AD33" s="26" t="inlineStr">
+        <is>
+          <t>MUZ-NXV2226</t>
+        </is>
+      </c>
+      <c r="AE33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="26" t="n"/>
+      <c r="AH33" s="26" t="n"/>
+      <c r="AI33" s="26" t="n">
+        <v>255</v>
+      </c>
+      <c r="AJ33" s="26" t="n">
+        <v>799</v>
+      </c>
+      <c r="AK33" s="26" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM33" s="26" t="n">
+        <v>800</v>
+      </c>
+      <c r="AN33" s="26" t="n">
+        <v>285</v>
+      </c>
+      <c r="AO33" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP33" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ33" s="26" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AR33" s="26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS33" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT33" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU33" s="26" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV33" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AW33" s="26" t="inlineStr">
+        <is>
+          <t>添付PDF仕様表から登録。消費電力は定格値。仕様書2025-09-19。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105.6" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>ルームエアコン</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>三菱電機</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>壁掛形</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>壁掛形</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>MSZ-NXV2826S-W</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>冷暖房用壁掛形ルームエアコン</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="26" t="n"/>
+      <c r="N34" s="26" t="n"/>
+      <c r="O34" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" s="26" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S34" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T34" s="26" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="U34" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y34" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z34" s="26" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AA34" s="26" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AB34" s="26" t="inlineStr">
+        <is>
+          <t>φ16（外径）</t>
+        </is>
+      </c>
+      <c r="AC34" s="26" t="inlineStr">
+        <is>
+          <t>MSZ-NXV2826S-W-IN</t>
+        </is>
+      </c>
+      <c r="AD34" s="26" t="inlineStr">
+        <is>
+          <t>MUZ-NXV2826S</t>
+        </is>
+      </c>
+      <c r="AE34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="26" t="n"/>
+      <c r="AH34" s="26" t="n"/>
+      <c r="AI34" s="26" t="n">
+        <v>255</v>
+      </c>
+      <c r="AJ34" s="26" t="n">
+        <v>799</v>
+      </c>
+      <c r="AK34" s="26" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM34" s="26" t="n">
+        <v>800</v>
+      </c>
+      <c r="AN34" s="26" t="n">
+        <v>285</v>
+      </c>
+      <c r="AO34" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP34" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="AQ34" s="26" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AR34" s="26" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AS34" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT34" s="26" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AU34" s="26" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV34" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AW34" s="26" t="inlineStr">
+        <is>
+          <t>添付PDF仕様表から登録。消費電力は定格値。仕様書2025-09-19。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>空冷ヒートポンプ式パッケージエアコン</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>三菱電機</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>ツイン</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>PEZX-ERMP280D6</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="n"/>
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="26" t="n"/>
+      <c r="N35" s="26" t="n"/>
+      <c r="O35" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="P35" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="26" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="S35" s="26" t="n"/>
+      <c r="T35" s="26" t="n"/>
+      <c r="U35" s="26" t="n"/>
+      <c r="V35" s="26" t="n"/>
+      <c r="W35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y35" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z35" s="26" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AA35" s="26" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AB35" s="26" t="n"/>
+      <c r="AC35" s="26" t="inlineStr">
+        <is>
+          <t>PE-RP140DA22</t>
+        </is>
+      </c>
+      <c r="AD35" s="26" t="inlineStr">
+        <is>
+          <t>PUZ-ERMP280KA6</t>
+        </is>
+      </c>
+      <c r="AE35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="26" t="n"/>
+      <c r="AH35" s="26" t="n"/>
+      <c r="AI35" s="26" t="n"/>
+      <c r="AJ35" s="26" t="n"/>
+      <c r="AK35" s="26" t="n"/>
+      <c r="AL35" s="26" t="n"/>
+      <c r="AM35" s="26" t="n"/>
+      <c r="AN35" s="26" t="n"/>
+      <c r="AO35" s="26" t="n"/>
+      <c r="AP35" s="26" t="n"/>
+      <c r="AQ35" s="26" t="n"/>
+      <c r="AR35" s="26" t="n"/>
+      <c r="AS35" s="26" t="n"/>
+      <c r="AT35" s="26" t="n"/>
+      <c r="AU35" s="26" t="n"/>
+      <c r="AV35" s="26" t="n"/>
+      <c r="AW35" s="26" t="inlineStr">
+        <is>
+          <t>セット定格値。冷媒配管は室外機側（液12.7/ガス25.4mm）。分岐後室内機側は各液9.52/ガス15.88mm。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>空冷ヒートポンプ式パッケージエアコン</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>ダイキン</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>SSRC160D</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="n"/>
+      <c r="L36" s="26" t="n"/>
+      <c r="M36" s="26" t="n"/>
+      <c r="N36" s="26" t="n"/>
+      <c r="O36" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="P36" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q36" s="26" t="n"/>
+      <c r="R36" s="26" t="n"/>
+      <c r="S36" s="26" t="n"/>
+      <c r="T36" s="26" t="n"/>
+      <c r="U36" s="26" t="n"/>
+      <c r="V36" s="26" t="n"/>
+      <c r="W36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y36" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="26" t="n"/>
+      <c r="AB36" s="26" t="n"/>
+      <c r="AC36" s="26" t="n"/>
+      <c r="AD36" s="26" t="n"/>
+      <c r="AE36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="26" t="n"/>
+      <c r="AH36" s="26" t="n"/>
+      <c r="AI36" s="26" t="n"/>
+      <c r="AJ36" s="26" t="n"/>
+      <c r="AK36" s="26" t="n"/>
+      <c r="AL36" s="26" t="n"/>
+      <c r="AM36" s="26" t="n"/>
+      <c r="AN36" s="26" t="n"/>
+      <c r="AO36" s="26" t="n"/>
+      <c r="AP36" s="26" t="n"/>
+      <c r="AQ36" s="26" t="n"/>
+      <c r="AR36" s="26" t="n"/>
+      <c r="AS36" s="26" t="n"/>
+      <c r="AT36" s="26" t="n"/>
+      <c r="AU36" s="26" t="n"/>
+      <c r="AV36" s="26" t="n"/>
+      <c r="AW36" s="26" t="inlineStr">
+        <is>
+          <t>メーカー仕様表JA16162409による。その他の数値は画像資料の細字照合未了のため保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>ルームエアコン</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>ダイキン</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
+      <c r="G37" s="26" t="n"/>
+      <c r="H37" s="26" t="n"/>
+      <c r="I37" s="26" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>AN716AFP-W</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="n"/>
+      <c r="L37" s="26" t="n"/>
+      <c r="M37" s="26" t="n"/>
+      <c r="N37" s="26" t="n"/>
+      <c r="O37" s="26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P37" s="26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q37" s="26" t="n"/>
+      <c r="R37" s="26" t="n"/>
+      <c r="S37" s="26" t="n"/>
+      <c r="T37" s="26" t="n"/>
+      <c r="U37" s="26" t="n"/>
+      <c r="V37" s="26" t="n"/>
+      <c r="W37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y37" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z37" s="26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA37" s="26" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AB37" s="26" t="n"/>
+      <c r="AC37" s="26" t="inlineStr">
+        <is>
+          <t>AN716AFP-W</t>
+        </is>
+      </c>
+      <c r="AD37" s="26" t="inlineStr">
+        <is>
+          <t>AR716AFP</t>
+        </is>
+      </c>
+      <c r="AE37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="26" t="n"/>
+      <c r="AH37" s="26" t="n"/>
+      <c r="AI37" s="26" t="n"/>
+      <c r="AJ37" s="26" t="n"/>
+      <c r="AK37" s="26" t="n"/>
+      <c r="AL37" s="26" t="n"/>
+      <c r="AM37" s="26" t="n"/>
+      <c r="AN37" s="26" t="n"/>
+      <c r="AO37" s="26" t="n"/>
+      <c r="AP37" s="26" t="n"/>
+      <c r="AQ37" s="26" t="n"/>
+      <c r="AR37" s="26" t="n"/>
+      <c r="AS37" s="26" t="n"/>
+      <c r="AT37" s="26" t="n"/>
+      <c r="AU37" s="26" t="n"/>
+      <c r="AV37" s="26" t="n"/>
+      <c r="AW37" s="26" t="inlineStr">
+        <is>
+          <t>メーカー仕様表JA16167008。定格能力。配管径は仕様表記載の液φ6.4/ガスφ12.7。消費電力は画像の精査未了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>空冷ヒートポンプ式パッケージエアコン</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>三菱電機</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>厨房用天吊形</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="26" t="n"/>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>シングル</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>PCZ-ZRMP140H6</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="n"/>
+      <c r="L38" s="26" t="n"/>
+      <c r="M38" s="26" t="n"/>
+      <c r="N38" s="26" t="n"/>
+      <c r="O38" s="26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P38" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S38" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T38" s="26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U38" s="26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V38" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y38" s="26" t="inlineStr">
+        <is>
+          <t>50/60</t>
+        </is>
+      </c>
+      <c r="Z38" s="26" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AA38" s="26" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="AB38" s="26" t="inlineStr">
+        <is>
+          <t>VP-25</t>
+        </is>
+      </c>
+      <c r="AC38" s="26" t="inlineStr">
+        <is>
+          <t>PC-RP140HA22</t>
+        </is>
+      </c>
+      <c r="AD38" s="26" t="inlineStr">
+        <is>
+          <t>PUZ-ZRMP140KA16</t>
+        </is>
+      </c>
+      <c r="AE38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="26" t="n"/>
+      <c r="AH38" s="26" t="n"/>
+      <c r="AI38" s="26" t="n">
+        <v>312</v>
+      </c>
+      <c r="AJ38" s="26" t="n">
+        <v>1520</v>
+      </c>
+      <c r="AK38" s="26" t="n">
+        <v>650</v>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>1338</v>
+      </c>
+      <c r="AM38" s="26" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AN38" s="26" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO38" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ38" s="26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AR38" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS38" s="26" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AT38" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU38" s="26" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="AV38" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW38" s="26" t="inlineStr">
+        <is>
+          <t>2026-02-13メーカー仕様書。定格標準値、50/60Hz共通。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AW27"/>
+  <autoFilter ref="A1:AW34"/>
   <dataValidations count="1">
     <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"確認済,要確認"</formula1>
@@ -5621,378 +6778,378 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.95" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="18.9" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>KUCHO_KIKI_MASTER 使用方法</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38.1" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>1行目：AutoCAD属性タグ／LISP用の英語キー</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>メーカー仕様書から抽出した機器情報を蓄積し、将来AutoCAD属性へ一括入力するためのマスターです。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38.1" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2行目：人が確認するための日本語項目名</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>KIKI_MASTERシート。1行＝1セット型番を基本とします。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38.1" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>3行目以降：機器マスターデータ</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>数値列には単位文字を入れず数値だけを保存します（例：冷房能力 7.1）。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38.1" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>案件固有情報</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>PAC-1等の機器記号、設置場所、数量はこのマスターには持たせず、案件側のAutoCAD属性で管理する想定です。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38.1" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>数値項目は単位をセル値に含めず、列見出し側に単位を記載します。</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>PDF自動抽出後は「要確認」、人が仕様書と照合したら「確認済」に変更します。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38.1" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>今後のLISP連携では1行目の英語タグをキーとして使用する想定です。</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>PLZ-HRMP80HF6をサンプル登録。室内機PL-HRP80HA5、室外機PUZ-HRMP80KA10、リモコンPAR-48MA等をPDFから転記しています。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26.1" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>KIKISET選択用列（2026-09-27）</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>KIKISETでは原則「機器種別 → メーカー → 現行・旧型 → シリーズ → 室内機タイプ → 吹出方式 → 能力クラス → システム構成 → セット形名」の順で絞り込みます。</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
     </row>
     <row r="11" ht="26.1" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>MODEL_STATUS</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>現行 / 旧型 / 不明。年式だけで自動判定せず、メーカー資料の現行ラインアップ・生産終了情報を優先します。</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>SERIES</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>メーカー固有のシリーズ名。例：ZR、スゴ暖、FIVE STAR ZEAS。シリーズ不明は空欄または不明。</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
     </row>
     <row r="13" ht="26.1" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>UNIT_TYPE</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>室内機タイプ。例：天井カセット、天井埋込、天吊、壁掛、床置。メーカー正式名称とは分離して検索用に正規化します。</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>AIRFLOW_TYPE</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>吹出方式。例：4方向、2方向、1方向。該当しない機種は空欄。</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>CAPACITY_CLASS</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>能力クラス。例：28、56、80、112、140。実能力[kW]とは別管理します。</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>SYSTEM_CONFIG</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>シングル / 同時ツイン / 同時トリプル / 同時フォー等。</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>MODEL</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>セット形名。KIKISETで最終的に選択する主キー候補です。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26.1" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>メーカー仕様書に記載された形式・正式名称を保存します。検索用のUNIT_TYPE/AIRFLOW_TYPEとは分離します。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>RELEASE_YEAR</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>発売年度。メーカー資料で確認できる場合のみ入力します。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>DISCONTINUED_YEAR</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>生産終了年度。メーカー資料で確認できる場合のみ入力します。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>SUCCESSOR_MODEL</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>旧型の後継セット形名。メーカー資料等で確認できた場合のみ入力します。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>PDF転記ルール</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>PDFにない値は推測せず空欄。資料不足・判定不能事項はNOTEへ「要確認」と記録します。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26.1" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>列キー運用</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>KIKISET/CAD連携は1行目の英語キーを参照し、列番号の固定参照は避けます。今後の列追加・並べ替えに耐えられる実装とします。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>KANKI_MASTER（換気機器マスター）</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>換気機器は1行＝1型番を基本とし、案件固有の機器記号・設置場所・数量は保持しません。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>KANKISET選択順</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>機器種別 → メーカー → 現行・旧型 → シリーズ → 取付方式 → 接続ダクト径 → 風量 → 型番 を基本とします。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>換気機器表への出力</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>機器表表示用の仕様文字列は、DUCT_DIA・AIRFLOW・STATIC_PRESSURE等の数値列からLISP側で組み立てます。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>案件固有情報</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>SYMBOL、LOCATION、QTY等は図面ブロック側で管理し、KANKI_MASTERには保存しません。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>列キー運用</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>KANKISET/CAD連携は1行目の英語キーを参照し、列番号固定で参照しないでください。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>REGISTERED_DATE</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>機器をマスターへ新規登録した日を YYYY-MM-DD 形式で保存します。KIKISETの「当日登録」一覧抽出に使用します。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>登録日入力ルール</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>新規機種追加時は登録当日の日付を入力します。既存機種の仕様修正だけでは登録日を変更しません。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>KANKI_MASTER 全熱交換器</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>全熱交換器は TEMP_EX_EFF（温度交換効率）、ENTHALPY_HEAT_EFF（エンタルピー交換効率 暖房）、ENTHALPY_COOL_EFF（エンタルピー交換効率 冷房）を使用。仕様書にない値は空欄。</t>
         </is>
@@ -6019,7 +7176,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="4"/>
@@ -6040,7 +7197,7 @@
     <col width="22" customWidth="1" min="27" max="29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
+    <row r="1" ht="27.9" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
           <t>EQUIP_TYPE</t>
@@ -6335,1259 +7492,1259 @@
       </c>
     </row>
     <row r="3" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="24" t="n"/>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>VD-10ZVC7</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>低騒音形 24時間換気機能付 定風量タイプ</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>24時間換気・定風量・強弱切替</t>
         </is>
       </c>
-      <c r="K3" s="26" t="n">
+      <c r="K3" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="L3" s="26" t="n">
+      <c r="L3" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="M3" s="26" t="n">
+      <c r="M3" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="N3" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="26" t="n">
+      <c r="N3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P3" s="24" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="n">
+      <c r="Q3" s="31" t="n">
         <v>0.0097</v>
       </c>
-      <c r="R3" s="29" t="n">
+      <c r="R3" s="31" t="n">
         <v>0.19</v>
       </c>
-      <c r="S3" s="24" t="n"/>
-      <c r="T3" s="29" t="n">
+      <c r="S3" s="21" t="n"/>
+      <c r="T3" s="31" t="n">
         <v>23.5</v>
       </c>
-      <c r="U3" s="26" t="n">
+      <c r="U3" s="23" t="n">
         <v>184</v>
       </c>
-      <c r="V3" s="26" t="n">
+      <c r="V3" s="23" t="n">
         <v>250</v>
       </c>
-      <c r="W3" s="26" t="n">
+      <c r="W3" s="23" t="n">
         <v>283</v>
       </c>
-      <c r="X3" s="29" t="n">
+      <c r="X3" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y3" s="24" t="n"/>
-      <c r="Z3" s="24" t="inlineStr">
+      <c r="Y3" s="21" t="n"/>
+      <c r="Z3" s="21" t="inlineStr">
         <is>
           <t>PDF仕様書から転記。仕様書作成日2024-02-01。EF-1設計点は100m3/h・90Pa。強運転時：消費電力9.7W、運転電流0.19A、騒音23.5dB、最大電流0.08A。24時間換気時：風量60m3/h、消費電力3.8W、騒音16.5dB。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="28" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
     </row>
     <row r="4" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>VD-15ZLC14-CS</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>低騒音形 24時間換気機能付</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>24時間換気・強弱切替</t>
         </is>
       </c>
-      <c r="K4" s="26" t="n">
+      <c r="K4" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="26" t="n">
+      <c r="L4" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="M4" s="26" t="n">
+      <c r="M4" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="N4" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="26" t="n">
+      <c r="N4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P4" s="24" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q4" s="29" t="n">
+      <c r="Q4" s="31" t="n">
         <v>0.014</v>
       </c>
-      <c r="R4" s="29" t="n">
+      <c r="R4" s="31" t="n">
         <v>0.15</v>
       </c>
-      <c r="S4" s="24" t="n"/>
-      <c r="T4" s="29" t="n">
+      <c r="S4" s="21" t="n"/>
+      <c r="T4" s="31" t="n">
         <v>28.5</v>
       </c>
-      <c r="U4" s="26" t="n">
+      <c r="U4" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="V4" s="26" t="n">
+      <c r="V4" s="23" t="n">
         <v>335</v>
       </c>
-      <c r="W4" s="26" t="n">
+      <c r="W4" s="23" t="n">
         <v>363</v>
       </c>
-      <c r="X4" s="29" t="n">
+      <c r="X4" s="31" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y4" s="24" t="n"/>
-      <c r="Z4" s="24" t="inlineStr">
+      <c r="Y4" s="21" t="n"/>
+      <c r="Z4" s="21" t="inlineStr">
         <is>
           <t>PDF仕様書から転記。EF-2設計点は120m3/h・50Pa。主要電気値は50Hz強運転時：消費電力14W、運転電流0.15A、騒音28.5dB。24時間換気時：風量90m3/h、消費電力5W、騒音16.5dB。60Hz強運転時：15.5W、0.165A。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="28" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
     </row>
     <row r="5" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>VD-20ZLC14-S</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>低騒音形 24時間換気機能付</t>
         </is>
       </c>
-      <c r="I5" s="24" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J5" s="24" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>24時間換気・強弱切替</t>
         </is>
       </c>
-      <c r="K5" s="26" t="n">
+      <c r="K5" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L5" s="26" t="n">
+      <c r="L5" s="23" t="n">
         <v>290</v>
       </c>
-      <c r="M5" s="26" t="n">
+      <c r="M5" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="N5" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="26" t="n">
+      <c r="N5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P5" s="24" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q5" s="29" t="n">
+      <c r="Q5" s="31" t="n">
         <v>0.044</v>
       </c>
-      <c r="R5" s="29" t="n">
+      <c r="R5" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="S5" s="24" t="n"/>
-      <c r="T5" s="29" t="n">
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="31" t="n">
         <v>36.5</v>
       </c>
-      <c r="U5" s="26" t="n">
+      <c r="U5" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="V5" s="26" t="n">
+      <c r="V5" s="23" t="n">
         <v>390</v>
       </c>
-      <c r="W5" s="26" t="n">
+      <c r="W5" s="23" t="n">
         <v>425</v>
       </c>
-      <c r="X5" s="29" t="n">
+      <c r="X5" s="31" t="n">
         <v>3.6</v>
       </c>
-      <c r="Y5" s="24" t="n"/>
-      <c r="Z5" s="24" t="inlineStr">
+      <c r="Y5" s="21" t="n"/>
+      <c r="Z5" s="21" t="inlineStr">
         <is>
           <t>PDF仕様書から転記。EF-3設計点は290m3/h・80Pa。主要電気値は50Hz強運転時：消費電力44W、運転電流0.5A、騒音36.5dB。24時間換気時：風量220m3/h、消費電力14.5W、騒音23dB。60Hz強運転時：49W、0.55A。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="28" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
     </row>
     <row r="6" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>VD-23ZLX14-CS</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>低騒音形 24時間換気機能付 インテリア格子タイプ</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>24時間換気・強弱切替</t>
         </is>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L6" s="26" t="n">
+      <c r="L6" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="M6" s="26" t="n">
+      <c r="M6" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="N6" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="26" t="n">
+      <c r="N6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="24" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="n">
+      <c r="Q6" s="31" t="n">
         <v>0.074</v>
       </c>
-      <c r="R6" s="29" t="n">
+      <c r="R6" s="31" t="n">
         <v>0.74</v>
       </c>
-      <c r="S6" s="24" t="n"/>
-      <c r="T6" s="29" t="n">
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="U6" s="26" t="n">
+      <c r="U6" s="23" t="n">
         <v>232</v>
       </c>
-      <c r="V6" s="26" t="n">
+      <c r="V6" s="23" t="n">
         <v>475</v>
       </c>
-      <c r="W6" s="26" t="n">
+      <c r="W6" s="23" t="n">
         <v>528</v>
       </c>
-      <c r="X6" s="29" t="n">
+      <c r="X6" s="31" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y6" s="24" t="n"/>
-      <c r="Z6" s="24" t="inlineStr">
+      <c r="Y6" s="21" t="n"/>
+      <c r="Z6" s="21" t="inlineStr">
         <is>
           <t>PDF仕様書から転記。EF-4設計点は400m3/h・150Pa。主要電気値は50Hz強運転時：消費電力74W、運転電流0.74A、騒音42dB。24時間換気時：風量310m3/h、消費電力28W、騒音27.5dB。60Hz強運転時：82W、0.82A。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="28" t="n"/>
+      <c r="AA6" s="25" t="n"/>
+      <c r="AB6" s="25" t="n"/>
+      <c r="AC6" s="25" t="n"/>
     </row>
     <row r="7" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>VD-18ZP14</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>低騒音形 オール金属タイプ</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J7" s="24" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K7" s="26" t="n">
+      <c r="K7" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L7" s="26" t="n">
+      <c r="L7" s="23" t="n">
         <v>250</v>
       </c>
-      <c r="M7" s="26" t="n">
+      <c r="M7" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="N7" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="26" t="n">
+      <c r="N7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q7" s="29" t="n">
+      <c r="Q7" s="31" t="n">
         <v>0.033</v>
       </c>
-      <c r="R7" s="29" t="n">
+      <c r="R7" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="S7" s="24" t="n"/>
-      <c r="T7" s="29" t="n">
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="31" t="n">
         <v>34.5</v>
       </c>
-      <c r="U7" s="26" t="n">
+      <c r="U7" s="23" t="n">
         <v>243</v>
       </c>
-      <c r="V7" s="26" t="n">
+      <c r="V7" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="W7" s="26" t="n">
+      <c r="W7" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="X7" s="29" t="n">
+      <c r="X7" s="31" t="n">
         <v>5.9</v>
       </c>
-      <c r="Y7" s="24" t="n"/>
-      <c r="Z7" s="24" t="inlineStr">
+      <c r="Y7" s="21" t="n"/>
+      <c r="Z7" s="21" t="inlineStr">
         <is>
           <t>PDF仕様書から転記。EF-5設計点は250m3/h・100Pa。主要電気値は50Hz定格時：消費電力33W、運転電流0.35A、騒音34.5dB。60Hz定格時：消費電力38W、運転電流0.4A、風量370m3/h。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="28" t="n"/>
+      <c r="AA7" s="25" t="n"/>
+      <c r="AB7" s="25" t="n"/>
+      <c r="AC7" s="25" t="n"/>
     </row>
     <row r="8" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>全熱交換器</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>ロスナイ</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>VL-200ZSD3</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>ダクト用ロスナイ</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>天井埋込形 急速排気機能付・電気式シャッター付</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>急速排気・ロスナイ換気切替</t>
         </is>
       </c>
-      <c r="K8" s="26" t="n">
+      <c r="K8" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="26" t="n">
+      <c r="L8" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="26" t="n">
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="24" t="n">
+      <c r="P8" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q8" s="29" t="n">
+      <c r="Q8" s="31" t="n">
         <v>0.0595</v>
       </c>
-      <c r="R8" s="29" t="n">
+      <c r="R8" s="31" t="n">
         <v>0.595</v>
       </c>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="29" t="n">
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="U8" s="26" t="n">
+      <c r="U8" s="23" t="n">
         <v>204</v>
       </c>
-      <c r="V8" s="26" t="n">
+      <c r="V8" s="23" t="n">
         <v>436</v>
       </c>
-      <c r="W8" s="26" t="n">
+      <c r="W8" s="23" t="n">
         <v>386</v>
       </c>
-      <c r="X8" s="29" t="n">
+      <c r="X8" s="31" t="n">
         <v>6.5</v>
       </c>
-      <c r="Y8" s="24" t="n"/>
-      <c r="Z8" s="24" t="inlineStr">
+      <c r="Y8" s="21" t="n"/>
+      <c r="Z8" s="21" t="inlineStr">
         <is>
           <t>出典: HEX-1_vl-200zsd3_2_sn.pdf。急速ノッチを主要値として登録（排気200m3/h、給気90m3/h、消費電力59.5W、電流0.595A、騒音43dB）。ロスナイノッチ時は排気60m3/h、給気48m3/h、消費電力23W、電流0.23A、騒音27dB。交換効率はロスナイノッチ時の値。仕様書作成日2021-02-15。</t>
         </is>
       </c>
-      <c r="AA8" s="28" t="n">
+      <c r="AA8" s="25" t="n">
         <v>76</v>
       </c>
-      <c r="AB8" s="28" t="n">
+      <c r="AB8" s="25" t="n">
         <v>63</v>
       </c>
-      <c r="AC8" s="28" t="n">
+      <c r="AC8" s="25" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="9" ht="63" customFormat="1" customHeight="1" s="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>全熱交換器</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>ロスナイ</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>LGH-N25CX3</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>業務用ロスナイ</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>天井カセット形マイコンタイプ</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>天井カセット</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>ロスナイ換気・普通換気切換、強・弱切換</t>
         </is>
       </c>
-      <c r="K9" s="26" t="n">
+      <c r="K9" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L9" s="26" t="n">
+      <c r="L9" s="23" t="n">
         <v>250</v>
       </c>
-      <c r="M9" s="26" t="n">
+      <c r="M9" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="N9" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="26" t="n">
+      <c r="N9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P9" s="24" t="n">
+      <c r="P9" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q9" s="29" t="n">
+      <c r="Q9" s="31" t="n">
         <v>0.128</v>
       </c>
-      <c r="R9" s="29" t="n">
+      <c r="R9" s="31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S9" s="24" t="n"/>
-      <c r="T9" s="29" t="n">
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="U9" s="26" t="n">
+      <c r="U9" s="23" t="n">
         <v>268</v>
       </c>
-      <c r="V9" s="26" t="n">
+      <c r="V9" s="23" t="n">
         <v>908</v>
       </c>
-      <c r="W9" s="26" t="n">
+      <c r="W9" s="23" t="n">
         <v>814</v>
       </c>
-      <c r="X9" s="29" t="n">
+      <c r="X9" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="Y9" s="24" t="n"/>
-      <c r="Z9" s="24" t="inlineStr">
+      <c r="Y9" s="21" t="n"/>
+      <c r="Z9" s="21" t="inlineStr">
         <is>
           <t>出典: HEX-2_lgh-n25cx3_2_sn.pdf。60Hz・ロスナイ換気の強ノッチを主要値として登録（排気250m3/h、機外静圧80Pa、消費電力128W、電流1.28A、騒音32dB）。弱ノッチは排気125m3/h・20Pa・81W・0.85A・25dB、微弱は排気85m3/h・9Pa・44W・0.44A・20dB。交換効率は強ノッチ。仕様書作成日2023-01-25。</t>
         </is>
       </c>
-      <c r="AA9" s="28" t="n">
+      <c r="AA9" s="25" t="n">
         <v>70.5</v>
       </c>
-      <c r="AB9" s="28" t="n">
+      <c r="AB9" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="AC9" s="28" t="n">
+      <c r="AC9" s="25" t="n">
         <v>61.5</v>
       </c>
     </row>
     <row r="10" ht="63" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>VD-20ZC14</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H10" s="24" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>低騒音形</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="23" t="n">
         <v>420</v>
       </c>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="26" t="n">
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P10" s="24" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q10" s="29" t="n">
+      <c r="Q10" s="31" t="n">
         <v>0.044</v>
       </c>
-      <c r="R10" s="29" t="n">
+      <c r="R10" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="29" t="n">
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="31" t="n">
         <v>36.5</v>
       </c>
-      <c r="U10" s="26" t="n">
+      <c r="U10" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="V10" s="26" t="n">
+      <c r="V10" s="23" t="n">
         <v>390</v>
       </c>
-      <c r="W10" s="26" t="n">
+      <c r="W10" s="23" t="n">
         <v>425</v>
       </c>
-      <c r="X10" s="29" t="n">
+      <c r="X10" s="31" t="n">
         <v>3.6</v>
       </c>
-      <c r="Y10" s="24" t="n"/>
-      <c r="Z10" s="24" t="inlineStr">
+      <c r="Y10" s="21" t="n"/>
+      <c r="Z10" s="21" t="inlineStr">
         <is>
           <t>出典: EF-2_vd-20zc14_0_sn.pdf。主要電気値は50Hz定格時：風量420m3/h、消費電力44W、運転電流0.5A、騒音36.5dB。60Hz定格時：風量420m3/h、消費電力49W、運転電流0.55A、騒音36.5dB。仕様書作成日2024-02-01。STATIC_PRESSUREは仕様表に設計点の明記がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="28" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="AA10" s="25" t="n"/>
+      <c r="AB10" s="25" t="n"/>
+      <c r="AC10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="409.6" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>VD-20ZP14</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>低騒音形 オール金属タイプ</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>天井埋込</t>
         </is>
       </c>
-      <c r="J11" s="24" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>強/弱</t>
         </is>
       </c>
-      <c r="K11" s="26" t="n">
+      <c r="K11" s="23" t="n">
         <v>150</v>
       </c>
-      <c r="L11" s="26" t="n">
+      <c r="L11" s="23" t="n">
         <v>520</v>
       </c>
-      <c r="M11" s="26" t="n"/>
-      <c r="N11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="26" t="n">
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P11" s="24" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q11" s="29" t="n">
+      <c r="Q11" s="31" t="n">
         <v>0.058</v>
       </c>
-      <c r="R11" s="29" t="n">
+      <c r="R11" s="31" t="n">
         <v>0.67</v>
       </c>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="29" t="n">
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="31" t="n">
         <v>44.5</v>
       </c>
-      <c r="U11" s="26" t="n">
+      <c r="U11" s="23" t="n">
         <v>243</v>
       </c>
-      <c r="V11" s="26" t="n">
+      <c r="V11" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="W11" s="26" t="n">
+      <c r="W11" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="X11" s="29" t="n">
+      <c r="X11" s="31" t="n">
         <v>6.3</v>
       </c>
-      <c r="Y11" s="24" t="n"/>
-      <c r="Z11" s="24" t="inlineStr">
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="21" t="inlineStr">
         <is>
           <t>出典: EF-2_vd-20zp14_0_sn.pdf。主要値は50Hz・強運転：風量520m3/h、消費電力58W、運転電流0.67A、騒音44.5dB。50Hz弱：330m3/h、28W、0.47A、33dB。60Hz強：520m3/h、66W、0.70A、44.5dB。60Hz弱：330m3/h、30W、0.49A、33dB。仕様書作成日2025-12-01。STATIC_PRESSUREは仕様表に単一の設計点記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。</t>
         </is>
       </c>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="28" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="AA11" s="25" t="n"/>
+      <c r="AB11" s="25" t="n"/>
+      <c r="AC11" s="25" t="n"/>
+    </row>
+    <row r="12" ht="409.6" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>EWF-35DSA2</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>低騒音形・排気タイプ</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J12" s="24" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n">
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n">
         <v>3600</v>
       </c>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="26" t="n">
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P12" s="24" t="n">
+      <c r="P12" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q12" s="29" t="n">
+      <c r="Q12" s="31" t="n">
         <v>0.175</v>
       </c>
-      <c r="R12" s="29" t="n">
+      <c r="R12" s="31" t="n">
         <v>1.78</v>
       </c>
-      <c r="S12" s="24" t="n">
+      <c r="S12" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="T12" s="29" t="n">
+      <c r="T12" s="31" t="n">
         <v>45.5</v>
       </c>
-      <c r="U12" s="26" t="n">
+      <c r="U12" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="V12" s="26" t="n">
+      <c r="V12" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="W12" s="26" t="n">
+      <c r="W12" s="23" t="n">
         <v>259</v>
       </c>
-      <c r="X12" s="29" t="n">
+      <c r="X12" s="31" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y12" s="24" t="n"/>
-      <c r="Z12" s="24" t="inlineStr">
+      <c r="Y12" s="21" t="n"/>
+      <c r="Z12" s="21" t="inlineStr">
         <is>
           <t>出典: EA-1_ewf-35dsa2_2_sn.pdf。排気専用。60Hz、単相100V。フリーエアー時：風量3600m3/h、消費電力175W、電流1.78A、騒音45.5dB。最大負荷電流2.84A、起動電流6.57A、公称出力150W。35cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="AA12" s="25" t="n"/>
+      <c r="AB12" s="25" t="n"/>
+      <c r="AC12" s="25" t="n"/>
+    </row>
+    <row r="13" ht="409.6" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>EWF-35DSA2-Q</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>低騒音形・給気タイプ</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J13" s="24" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K13" s="26" t="n"/>
-      <c r="L13" s="26" t="n">
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n">
         <v>3600</v>
       </c>
-      <c r="M13" s="26" t="n"/>
-      <c r="N13" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="26" t="n">
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="P13" s="24" t="n">
+      <c r="P13" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q13" s="29" t="n">
+      <c r="Q13" s="31" t="n">
         <v>0.181</v>
       </c>
-      <c r="R13" s="29" t="n">
+      <c r="R13" s="31" t="n">
         <v>1.82</v>
       </c>
-      <c r="S13" s="24" t="n">
+      <c r="S13" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="T13" s="29" t="n">
+      <c r="T13" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="U13" s="26" t="n">
+      <c r="U13" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="V13" s="26" t="n">
+      <c r="V13" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="W13" s="26" t="n">
+      <c r="W13" s="23" t="n">
         <v>259</v>
       </c>
-      <c r="X13" s="29" t="n">
+      <c r="X13" s="31" t="n">
         <v>9.5</v>
       </c>
-      <c r="Y13" s="24" t="n"/>
-      <c r="Z13" s="24" t="inlineStr">
+      <c r="Y13" s="21" t="n"/>
+      <c r="Z13" s="21" t="inlineStr">
         <is>
           <t>出典: OA-1_ewf-35dsa2-q_2_sn.pdf。給気専用。60Hz、単相100V。フリーエアー時：風量3600m3/h、消費電力181W、電流1.82A、騒音53dB。最大負荷電流2.45A、起動電流5.75A、公称出力150W。35cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="28" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="AA13" s="25" t="n"/>
+      <c r="AB13" s="25" t="n"/>
+      <c r="AC13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="409.6" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>EWF-35DTA2</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>低騒音形・排気タイプ</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n">
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n">
         <v>3600</v>
       </c>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="24" t="n">
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="O14" s="26" t="n">
+      <c r="O14" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="P14" s="24" t="n">
+      <c r="P14" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q14" s="29" t="n">
+      <c r="Q14" s="31" t="n">
         <v>0.168</v>
       </c>
-      <c r="R14" s="29" t="n">
+      <c r="R14" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="S14" s="24" t="n">
+      <c r="S14" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="T14" s="29" t="n">
+      <c r="T14" s="31" t="n">
         <v>45.5</v>
       </c>
-      <c r="U14" s="26" t="n">
+      <c r="U14" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="V14" s="26" t="n">
+      <c r="V14" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="W14" s="26" t="n">
+      <c r="W14" s="23" t="n">
         <v>259</v>
       </c>
-      <c r="X14" s="29" t="n">
+      <c r="X14" s="31" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y14" s="24" t="n"/>
-      <c r="Z14" s="24" t="inlineStr">
+      <c r="Y14" s="21" t="n"/>
+      <c r="Z14" s="21" t="inlineStr">
         <is>
           <t>出典: EA-1_ewf-35dta2_2_sn.pdf。排気専用。60Hz、三相200-220V。200Vフリーエアー時：風量3600m3/h、消費電力168W、電流0.75A、騒音45.5dB。220V時：消費電力176W、電流0.80A。最大負荷電流1.06-1.05A、起動電流3.63-3.97A、公称出力150W。35cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA14" s="28" t="n"/>
-      <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="AA14" s="25" t="n"/>
+      <c r="AB14" s="25" t="n"/>
+      <c r="AC14" s="25" t="n"/>
+    </row>
+    <row r="15" ht="409.6" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>EWF-35DTA2-Q</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>低騒音形・給気タイプ</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="26" t="n">
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n">
         <v>3600</v>
       </c>
-      <c r="M15" s="26" t="n"/>
-      <c r="N15" s="24" t="n">
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="26" t="n">
+      <c r="O15" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="P15" s="24" t="n">
+      <c r="P15" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="Q15" s="29" t="n">
+      <c r="Q15" s="31" t="n">
         <v>0.174</v>
       </c>
-      <c r="R15" s="29" t="n">
+      <c r="R15" s="31" t="n">
         <v>0.72</v>
       </c>
-      <c r="S15" s="24" t="n">
+      <c r="S15" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="T15" s="29" t="n">
+      <c r="T15" s="31" t="n">
         <v>52.5</v>
       </c>
-      <c r="U15" s="26" t="n">
+      <c r="U15" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="V15" s="26" t="n">
+      <c r="V15" s="23" t="n">
         <v>470</v>
       </c>
-      <c r="W15" s="26" t="n">
+      <c r="W15" s="23" t="n">
         <v>259</v>
       </c>
-      <c r="X15" s="29" t="n">
+      <c r="X15" s="31" t="n">
         <v>9.5</v>
       </c>
-      <c r="Y15" s="24" t="n"/>
-      <c r="Z15" s="24" t="inlineStr">
+      <c r="Y15" s="21" t="n"/>
+      <c r="Z15" s="21" t="inlineStr">
         <is>
           <t>出典: OA-1_ewf-35dta2-q_2_sn.pdf。給気専用。60Hz、三相200-220V。200Vフリーエアー時：風量3600m3/h、消費電力174W、電流0.72A、騒音52.5dB。220V時：消費電力178W、電流0.74A、騒音53dB。最大負荷電流1.05A、起動電流3.59-3.96A、公称出力150W。35cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA15" s="28" t="n"/>
-      <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="28" t="n"/>
-    </row>
-    <row r="16">
+      <c r="AA15" s="25" t="n"/>
+      <c r="AB15" s="25" t="n"/>
+      <c r="AC15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="409.6" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
@@ -7652,14 +8809,14 @@
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q16" s="30" t="n">
+      <c r="Q16" s="32" t="n">
         <v>0.018</v>
       </c>
-      <c r="R16" s="30" t="n">
+      <c r="R16" s="32" t="n">
         <v>0.37</v>
       </c>
       <c r="S16" s="9" t="n"/>
-      <c r="T16" s="30" t="n">
+      <c r="T16" s="32" t="n">
         <v>38</v>
       </c>
       <c r="U16" s="11" t="n">
@@ -7671,7 +8828,7 @@
       <c r="W16" s="11" t="n">
         <v>362</v>
       </c>
-      <c r="X16" s="30" t="n">
+      <c r="X16" s="32" t="n">
         <v>3.2</v>
       </c>
       <c r="Y16" s="9" t="n"/>
@@ -7684,7 +8841,7 @@
       <c r="AB16" s="13" t="n"/>
       <c r="AC16" s="13" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="409.6" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>ダクト用換気扇</t>
@@ -7749,14 +8906,14 @@
           <t>50/60</t>
         </is>
       </c>
-      <c r="Q17" s="30" t="n">
+      <c r="Q17" s="32" t="n">
         <v>0.095</v>
       </c>
-      <c r="R17" s="30" t="n">
+      <c r="R17" s="32" t="n">
         <v>1.6</v>
       </c>
       <c r="S17" s="9" t="n"/>
-      <c r="T17" s="30" t="n">
+      <c r="T17" s="32" t="n">
         <v>52</v>
       </c>
       <c r="U17" s="11" t="n">
@@ -7768,7 +8925,7 @@
       <c r="W17" s="11" t="n">
         <v>428</v>
       </c>
-      <c r="X17" s="30" t="n">
+      <c r="X17" s="32" t="n">
         <v>7</v>
       </c>
       <c r="Y17" s="9" t="n"/>
@@ -7781,195 +8938,195 @@
       <c r="AB17" s="13" t="n"/>
       <c r="AC17" s="13" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+    <row r="18" ht="409.6" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>EWF-20YSA2</t>
         </is>
       </c>
-      <c r="G18" s="31" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H18" s="31" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>低騒音形・排気タイプ</t>
         </is>
       </c>
-      <c r="I18" s="31" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J18" s="31" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K18" s="33" t="n"/>
-      <c r="L18" s="33" t="n">
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n">
         <v>780</v>
       </c>
-      <c r="M18" s="33" t="n"/>
-      <c r="N18" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="33" t="n">
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P18" s="31" t="n">
+      <c r="P18" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="Q18" s="34" t="n">
+      <c r="Q18" s="32" t="n">
         <v>0.028</v>
       </c>
-      <c r="R18" s="34" t="n">
+      <c r="R18" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="S18" s="31" t="n">
+      <c r="S18" s="9" t="n">
         <v>0.015</v>
       </c>
-      <c r="T18" s="34" t="n">
+      <c r="T18" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="U18" s="33" t="n">
+      <c r="U18" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="V18" s="33" t="n">
+      <c r="V18" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="W18" s="33" t="n">
+      <c r="W18" s="11" t="n">
         <v>197</v>
       </c>
-      <c r="X18" s="34" t="n">
+      <c r="X18" s="32" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y18" s="31" t="n"/>
-      <c r="Z18" s="31" t="inlineStr">
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="9" t="inlineStr">
         <is>
           <t>出典: EA-1ewf-20ysa2_2_sn.pdf。排気専用。60Hz、単相100V。フリーエアー時：風量780m3/h、消費電力28W、電流0.30A、騒音31dB。最大負荷電流0.37A、起動電流0.64A、公称出力15W。20cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA18" s="35" t="n"/>
-      <c r="AB18" s="35" t="n"/>
-      <c r="AC18" s="35" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="13" t="n"/>
+      <c r="AC18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="409.6" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>三菱電機</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>EWF-20YSA2-Q</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>産業用有圧換気扇</t>
         </is>
       </c>
-      <c r="H19" s="31" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>低騒音形・給気タイプ</t>
         </is>
       </c>
-      <c r="I19" s="31" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>壁取付</t>
         </is>
       </c>
-      <c r="J19" s="31" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>定格運転</t>
         </is>
       </c>
-      <c r="K19" s="33" t="n"/>
-      <c r="L19" s="33" t="n">
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n">
         <v>780</v>
       </c>
-      <c r="M19" s="33" t="n"/>
-      <c r="N19" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="33" t="n">
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P19" s="31" t="n">
+      <c r="P19" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="Q19" s="34" t="n">
+      <c r="Q19" s="32" t="n">
         <v>0.033</v>
       </c>
-      <c r="R19" s="34" t="n">
+      <c r="R19" s="32" t="n">
         <v>0.34</v>
       </c>
-      <c r="S19" s="31" t="n">
+      <c r="S19" s="9" t="n">
         <v>0.015</v>
       </c>
-      <c r="T19" s="34" t="n">
+      <c r="T19" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="U19" s="33" t="n">
+      <c r="U19" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="V19" s="33" t="n">
+      <c r="V19" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="W19" s="33" t="n">
+      <c r="W19" s="11" t="n">
         <v>197</v>
       </c>
-      <c r="X19" s="34" t="n">
+      <c r="X19" s="32" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="31" t="inlineStr">
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="inlineStr">
         <is>
           <t>出典: OA-1ewf-20ysa2-q_2_sn.pdf。給気専用。60Hz、単相100V。フリーエアー時：風量780m3/h、消費電力33W、電流0.34A、騒音37dB。最大負荷電流0.41A、起動電流0.69A、公称出力15W。20cm金属製軸流羽根。STATIC_PRESSUREは単一設計点の記載がないため空欄。MODEL_STATUSは資料内に現行/旧型の明記がないため不明。仕様書作成日2022-03-24。</t>
         </is>
       </c>
-      <c r="AA19" s="35" t="n"/>
-      <c r="AB19" s="35" t="n"/>
-      <c r="AC19" s="35" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="13" t="n"/>
+      <c r="AC19" s="13" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:Y2"/>
@@ -7984,7 +9141,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
@@ -7994,7 +9151,7 @@
     <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
+    <row r="1" ht="27.9" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>SHAPE</t>
@@ -8066,7 +9223,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27.95" customHeight="1">
+    <row r="2" ht="27.9" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>形状</t>
@@ -8192,7 +9349,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N3" s="36" t="n">
+      <c r="N3" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8250,7 +9407,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N4" s="36" t="n">
+      <c r="N4" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8308,7 +9465,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N5" s="36" t="n">
+      <c r="N5" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8366,7 +9523,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N6" s="36" t="n">
+      <c r="N6" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8424,7 +9581,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N7" s="36" t="n">
+      <c r="N7" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8482,7 +9639,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N8" s="36" t="n">
+      <c r="N8" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8542,7 +9699,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N9" s="36" t="n">
+      <c r="N9" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8602,7 +9759,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N10" s="36" t="n">
+      <c r="N10" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8662,7 +9819,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N11" s="36" t="n">
+      <c r="N11" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8722,7 +9879,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IB/2411876ha9102_ibim.pdf</t>
         </is>
       </c>
-      <c r="N12" s="36" t="n">
+      <c r="N12" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8782,7 +9939,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N13" s="36" t="n">
+      <c r="N13" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8842,7 +9999,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N14" s="36" t="n">
+      <c r="N14" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8902,7 +10059,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N15" s="36" t="n">
+      <c r="N15" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -8962,7 +10119,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N16" s="36" t="n">
+      <c r="N16" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9022,7 +10179,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N17" s="36" t="n">
+      <c r="N17" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9084,7 +10241,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N18" s="36" t="n">
+      <c r="N18" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9146,7 +10303,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N19" s="36" t="n">
+      <c r="N19" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9208,7 +10365,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N20" s="36" t="n">
+      <c r="N20" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9270,7 +10427,7 @@
           <t>https://dl.mitsubishielectric.co.jp/dl/ldg/wink/ssl/wink_doc/m_contents/wink/FAN_IM/2411876hb6902_ibim.pdf</t>
         </is>
       </c>
-      <c r="N21" s="36" t="n">
+      <c r="N21" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9332,7 +10489,7 @@
           <t>https://www.mitsubishielectric.co.jp/ldg/wink/ssl/displayProduct.do?pid=129409</t>
         </is>
       </c>
-      <c r="N22" s="36" t="n">
+      <c r="N22" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9392,7 +10549,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N23" s="36" t="n">
+      <c r="N23" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9452,7 +10609,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N24" s="36" t="n">
+      <c r="N24" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9512,7 +10669,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N25" s="36" t="n">
+      <c r="N25" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9572,7 +10729,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N26" s="36" t="n">
+      <c r="N26" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9632,7 +10789,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N27" s="36" t="n">
+      <c r="N27" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9692,7 +10849,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N28" s="36" t="n">
+      <c r="N28" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9752,7 +10909,7 @@
           <t>https://www.unix-coltd.co.jp/wp-content/themes/neos/product_files/download_files/BSW-SB10M-draw.pdf</t>
         </is>
       </c>
-      <c r="N29" s="36" t="n">
+      <c r="N29" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -9782,7 +10939,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="3"/>
@@ -9792,7 +10949,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
+    <row r="1" ht="27.9" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>MODEL</t>
@@ -9829,7 +10986,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="27.95" customHeight="1">
+    <row r="2" ht="27.9" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>室内給気口品番</t>
@@ -9893,7 +11050,7 @@
           <t>https://www.mitsubishielectric.co.jp/ldg/wink/ssl/displayProduct.do?pid=142540</t>
         </is>
       </c>
-      <c r="G3" s="36" t="n">
+      <c r="G3" s="33" t="n">
         <v>46298</v>
       </c>
     </row>
@@ -10166,13 +11323,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FF998E-7C31-4A11-9CDF-F0AA18773FF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16CD0F98-B232-4953-8298-D84F499927BD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BFDFD3-EDAE-4CEA-A7C6-CA336E2D236C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67952C0-63BD-4C0F-9EE5-31E4F7ED9186}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66E3E459-1492-43E4-BAC4-06AFDBFA4ACB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09F57733-6BF1-4725-8042-6286FD71CAAF}"/>
 </file>